--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125902935</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125902904</v>
+        <v>125903158</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561628</v>
+        <v>561527</v>
       </c>
       <c r="R5" t="n">
-        <v>6967736</v>
+        <v>6967841</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125903158</v>
+        <v>125902904</v>
       </c>
       <c r="B6" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561527</v>
+        <v>561628</v>
       </c>
       <c r="R6" t="n">
-        <v>6967841</v>
+        <v>6967736</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125902935</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125903050</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125903158</v>
+        <v>125902904</v>
       </c>
       <c r="B5" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561527</v>
+        <v>561628</v>
       </c>
       <c r="R5" t="n">
-        <v>6967841</v>
+        <v>6967736</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125902904</v>
+        <v>125903158</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561628</v>
+        <v>561527</v>
       </c>
       <c r="R6" t="n">
-        <v>6967736</v>
+        <v>6967841</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125902935</v>
       </c>
       <c r="B3" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125902935</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125903050</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125902904</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125903158</v>
       </c>
       <c r="B6" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125902935</v>
       </c>
       <c r="B3" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125902853</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125902935</v>
       </c>
       <c r="B3" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125903050</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125902904</v>
+        <v>125903158</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561628</v>
+        <v>561527</v>
       </c>
       <c r="R5" t="n">
-        <v>6967736</v>
+        <v>6967841</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125903158</v>
+        <v>125902904</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561527</v>
+        <v>561628</v>
       </c>
       <c r="R6" t="n">
-        <v>6967841</v>
+        <v>6967736</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125903158</v>
+        <v>125902904</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561527</v>
+        <v>561628</v>
       </c>
       <c r="R5" t="n">
-        <v>6967841</v>
+        <v>6967736</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125902904</v>
+        <v>125903158</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561628</v>
+        <v>561527</v>
       </c>
       <c r="R6" t="n">
-        <v>6967736</v>
+        <v>6967841</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125902935</v>
       </c>
       <c r="B3" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125902935</v>
       </c>
       <c r="B3" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125902904</v>
+        <v>125903158</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561628</v>
+        <v>561527</v>
       </c>
       <c r="R5" t="n">
-        <v>6967736</v>
+        <v>6967841</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125903158</v>
+        <v>125902904</v>
       </c>
       <c r="B6" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561527</v>
+        <v>561628</v>
       </c>
       <c r="R6" t="n">
-        <v>6967841</v>
+        <v>6967736</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125902853</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125902935</v>
       </c>
       <c r="B3" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125903050</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125903158</v>
+        <v>125902904</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561527</v>
+        <v>561628</v>
       </c>
       <c r="R5" t="n">
-        <v>6967841</v>
+        <v>6967736</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125902904</v>
+        <v>125903158</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>80080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561628</v>
+        <v>561527</v>
       </c>
       <c r="R6" t="n">
-        <v>6967736</v>
+        <v>6967841</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125902935</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125902904</v>
+        <v>125903158</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561628</v>
+        <v>561527</v>
       </c>
       <c r="R5" t="n">
-        <v>6967736</v>
+        <v>6967841</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125903158</v>
+        <v>125902904</v>
       </c>
       <c r="B6" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561527</v>
+        <v>561628</v>
       </c>
       <c r="R6" t="n">
-        <v>6967841</v>
+        <v>6967736</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125902853</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125902935</v>
       </c>
       <c r="B3" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125903050</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125903158</v>
       </c>
       <c r="B5" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125902904</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>125903158</v>
       </c>
       <c r="B5" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>125903158</v>
       </c>
       <c r="B5" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>125903158</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>125903158</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>125903158</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>125903158</v>
       </c>
       <c r="B5" t="n">
-        <v>80114</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125902853</v>
+        <v>125902904</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561637</v>
+        <v>561628</v>
       </c>
       <c r="R2" t="n">
-        <v>6967726</v>
+        <v>6967736</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125902935</v>
+        <v>125903050</v>
       </c>
       <c r="B3" t="n">
-        <v>98382</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561609</v>
+        <v>561554</v>
       </c>
       <c r="R3" t="n">
-        <v>6967734</v>
+        <v>6967820</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125903050</v>
+        <v>125903158</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,34 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ol-Olstorpet, Ol-Olstorpet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561554</v>
+        <v>561527</v>
       </c>
       <c r="R4" t="n">
-        <v>6967820</v>
+        <v>6967841</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -953,6 +951,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -971,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125903158</v>
+        <v>125902853</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,40 +981,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ol-Olstorpet, Ol-Olstorpet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561527</v>
+        <v>561637</v>
       </c>
       <c r="R5" t="n">
-        <v>6967841</v>
+        <v>6967726</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1047,13 +1043,17 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1072,32 +1072,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125902904</v>
+        <v>125902935</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>99140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561628</v>
+        <v>561609</v>
       </c>
       <c r="R6" t="n">
-        <v>6967736</v>
+        <v>6967734</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 21441-2025 artfynd.xlsx
+++ b/artfynd/A 21441-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125902904</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125903050</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125903158</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125902853</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,8 +1191,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125902935</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>